--- a/03_Outputs/all/01_TablasDescriptivas/idx1_servicio.xlsx
+++ b/03_Outputs/all/01_TablasDescriptivas/idx1_servicio.xlsx
@@ -396,7 +396,7 @@
         <v>123</v>
       </c>
       <c r="C2">
-        <v>-5.526016260162601</v>
+        <v>-5.526016260162602</v>
       </c>
       <c r="D2">
         <v>10.98383937620887</v>
@@ -418,7 +418,7 @@
         <v>123</v>
       </c>
       <c r="C3">
-        <v>-2.374796747967479</v>
+        <v>-2.37479674796748</v>
       </c>
       <c r="D3">
         <v>9.261506741911985</v>
